--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_silicon/harmonized.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_silicon/harmonized.xlsx
@@ -432,7 +432,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8926,12 +8926,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8978,12 +8978,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10278,12 +10278,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10382,12 +10382,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11162,12 +11162,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11370,12 +11370,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11422,12 +11422,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11682,12 +11682,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11786,12 +11786,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -11942,12 +11942,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -11994,12 +11994,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12306,12 +12306,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12358,12 +12358,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12514,12 +12514,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12566,12 +12566,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12670,12 +12670,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12774,12 +12774,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -12826,12 +12826,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -12982,12 +12982,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13034,12 +13034,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13190,12 +13190,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13294,12 +13294,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13346,12 +13346,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13398,12 +13398,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13450,12 +13450,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13554,12 +13554,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13606,12 +13606,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13658,12 +13658,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -13814,12 +13814,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -13866,12 +13866,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -13918,12 +13918,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -13970,12 +13970,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -14022,12 +14022,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14126,12 +14126,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14178,12 +14178,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14230,12 +14230,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14282,12 +14282,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14490,12 +14490,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14542,12 +14542,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -14594,12 +14594,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -14646,12 +14646,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -14802,12 +14802,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -15010,12 +15010,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -15062,12 +15062,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -15114,12 +15114,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -15322,12 +15322,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15426,12 +15426,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15530,12 +15530,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15582,12 +15582,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -15634,12 +15634,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -15686,12 +15686,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -15738,12 +15738,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -15790,12 +15790,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -15842,12 +15842,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -15894,12 +15894,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -15946,12 +15946,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -16050,12 +16050,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -16102,12 +16102,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -16154,12 +16154,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -16206,12 +16206,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -16310,12 +16310,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -16362,12 +16362,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -16466,12 +16466,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -16518,12 +16518,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -16570,12 +16570,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -16622,12 +16622,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -16674,12 +16674,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
